--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_08/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_08/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>40.21016628507971</v>
+        <v>43.05068280090355</v>
       </c>
       <c r="B2" t="n">
-        <v>96.03997941885335</v>
+        <v>75.64395888371739</v>
       </c>
       <c r="C2" t="n">
-        <v>45.92808962993951</v>
+        <v>40.00441977211329</v>
       </c>
       <c r="D2" t="n">
-        <v>8.168703619226088</v>
+        <v>8.427766118160518</v>
       </c>
       <c r="E2" t="n">
-        <v>4.340219083976546</v>
+        <v>4.807117777741808</v>
       </c>
       <c r="F2" t="n">
-        <v>3.366124013626187</v>
+        <v>3.694451453577154</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2850184663756352</v>
+        <v>0.2148500980899601</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02863576107443952</v>
+        <v>-0.09477910511405589</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5258161163370026</v>
+        <v>-0.5528033414880295</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3289749913699965</v>
+        <v>-0.3906945606312388</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.001512736466339064</v>
+        <v>-0.006821511763075021</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.51699799644626</v>
+        <v>-0.5370045520060236</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0005949407120139999</v>
+        <v>-0.0009944487254912038</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>40.21016628507971</v>
+        <v>99.99522073686744</v>
       </c>
       <c r="B3" t="n">
-        <v>95.21483737539477</v>
+        <v>75.69475467747611</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92808962993951</v>
+        <v>40.00563457351308</v>
       </c>
       <c r="D3" t="n">
-        <v>8.168703619226088</v>
+        <v>7.49957364827298</v>
       </c>
       <c r="E3" t="n">
-        <v>3.569900886396152</v>
+        <v>4.680765774634185</v>
       </c>
       <c r="F3" t="n">
-        <v>3.366124013626187</v>
+        <v>10.63897918388137</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2850184663756352</v>
+        <v>0.01073455885025907</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02863576107443952</v>
+        <v>-0.9212511386579915</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5258161163370026</v>
+        <v>-0.9455094203924282</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3289749913699965</v>
+        <v>-0.9759494029257373</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.001512736466339064</v>
+        <v>-0.01205015177913037</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.51699799644626</v>
+        <v>-0.5874659477501805</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0005949407120139999</v>
+        <v>-0.001267779040442785</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999999174514</v>
+        <v>43.05068280090355</v>
       </c>
       <c r="B4" t="n">
-        <v>137.6141544653134</v>
+        <v>75.64395888371739</v>
       </c>
       <c r="C4" t="n">
-        <v>46.0963011989612</v>
+        <v>40.00441977211329</v>
       </c>
       <c r="D4" t="n">
-        <v>6.290844631181365</v>
+        <v>8.427766118160518</v>
       </c>
       <c r="E4" t="n">
-        <v>3.066216784016316</v>
+        <v>4.807484906872447</v>
       </c>
       <c r="F4" t="n">
-        <v>10.39848294072529</v>
+        <v>3.694451453577154</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01088592003406524</v>
+        <v>0.2148500980899601</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9308839430361965</v>
+        <v>-0.09477910511405589</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9521608290492426</v>
+        <v>-0.5528033414880295</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.979731774771502</v>
+        <v>-0.3906945606312388</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.006257788767106144</v>
+        <v>-0.006821511763075021</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069729323717</v>
+        <v>-0.5370045520060236</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0151225165993796</v>
+        <v>-0.0009944487254912038</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48.79576929635138</v>
+        <v>68.07329662796644</v>
       </c>
       <c r="B5" t="n">
-        <v>110.774959797176</v>
+        <v>174.7012355872982</v>
       </c>
       <c r="C5" t="n">
-        <v>46.11874975567591</v>
+        <v>40.00442476443024</v>
       </c>
       <c r="D5" t="n">
-        <v>7.397504036995773</v>
+        <v>11.17858698169154</v>
       </c>
       <c r="E5" t="n">
-        <v>4.174712081622427</v>
+        <v>4.806650614166463</v>
       </c>
       <c r="F5" t="n">
-        <v>4.19705332239863</v>
+        <v>6.178548747480805</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1356761889045218</v>
+        <v>0.04134047317894268</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4528447953032125</v>
+        <v>-0.7609380061365872</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7065936927636908</v>
+        <v>-0.850614734513963</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6872047468072289</v>
+        <v>-0.8954337773526507</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.05576248156814309</v>
+        <v>-0.01419457690912069</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5740069325954024</v>
+        <v>-0.3600222384742608</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01650737445450138</v>
+        <v>-0.0009955719968038346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51.48369980040371</v>
+        <v>63.97335521971433</v>
       </c>
       <c r="B6" t="n">
-        <v>117.1657611661799</v>
+        <v>99.00166693439326</v>
       </c>
       <c r="C6" t="n">
-        <v>45.926092138986</v>
+        <v>40.06855470119889</v>
       </c>
       <c r="D6" t="n">
-        <v>10.93693013168759</v>
+        <v>11.41645782149636</v>
       </c>
       <c r="E6" t="n">
-        <v>3.729452171339113</v>
+        <v>4.361526051612371</v>
       </c>
       <c r="F6" t="n">
-        <v>4.474011618917086</v>
+        <v>5.709811278365372</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1175216989367494</v>
+        <v>0.05194754053189068</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5269572543226343</v>
+        <v>-0.7163630162977289</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7384803168710004</v>
+        <v>-0.828628895708394</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.74120950141627</v>
+        <v>-0.8692288604776028</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05755249615831862</v>
+        <v>-0.04435475542729431</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.337245953222314</v>
+        <v>-0.3548001641478574</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0003066269598281009</v>
+        <v>-0.0154248077697508</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73.62816748478826</v>
+        <v>44.0831859465129</v>
       </c>
       <c r="B7" t="n">
-        <v>110.5556347022473</v>
+        <v>74.99973207581556</v>
       </c>
       <c r="C7" t="n">
-        <v>46.4931155359439</v>
+        <v>40.0578574664694</v>
       </c>
       <c r="D7" t="n">
-        <v>10.26950423493503</v>
+        <v>8.273265040635637</v>
       </c>
       <c r="E7" t="n">
-        <v>3.992225580562764</v>
+        <v>4.352057560743544</v>
       </c>
       <c r="F7" t="n">
-        <v>6.788868306160202</v>
+        <v>3.78426463727163</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0316813588500642</v>
+        <v>0.1960868344498581</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8336949078340828</v>
+        <v>-0.1563256505442346</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8909312920943944</v>
+        <v>-0.5779653461364812</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9352873723009042</v>
+        <v>-0.445173468466827</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1523393072661197</v>
+        <v>-0.0005753217071890553</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4250075451990959</v>
+        <v>-0.5438879063100861</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03085760833752894</v>
+        <v>-0.01301792995561463</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>42.87944735823455</v>
+        <v>53.56048801722266</v>
       </c>
       <c r="B8" t="n">
-        <v>95.79495558320377</v>
+        <v>99.94144334119338</v>
       </c>
       <c r="C8" t="n">
-        <v>45.92851109866206</v>
+        <v>40.06154338314446</v>
       </c>
       <c r="D8" t="n">
-        <v>8.001526198514476</v>
+        <v>7.49957364827298</v>
       </c>
       <c r="E8" t="n">
-        <v>4.30437150915512</v>
+        <v>4.577070163464827</v>
       </c>
       <c r="F8" t="n">
-        <v>3.615186923145988</v>
+        <v>4.821747460704669</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2224794648016961</v>
+        <v>0.09368052746256109</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.197436570532935</v>
+        <v>-0.5239081149518601</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5946074297936276</v>
+        <v>-0.7388738183673728</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4794507768620747</v>
+        <v>-0.7402990838602396</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.03094961939366153</v>
+        <v>-0.02262609536993889</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5347221882198393</v>
+        <v>-0.5892164241090769</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0006557746440103281</v>
+        <v>-0.01384726120750385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63.53393964037869</v>
+        <v>86.74332272971444</v>
       </c>
       <c r="B9" t="n">
-        <v>110.9300515325838</v>
+        <v>75.61670729553559</v>
       </c>
       <c r="C9" t="n">
-        <v>46.06443144513196</v>
+        <v>40.00094193992818</v>
       </c>
       <c r="D9" t="n">
-        <v>10.59478466349825</v>
+        <v>9.35601808399913</v>
       </c>
       <c r="E9" t="n">
-        <v>4.231729566367986</v>
+        <v>4.661466370168496</v>
       </c>
       <c r="F9" t="n">
-        <v>5.531595127165447</v>
+        <v>8.607294356183253</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05413671401537025</v>
+        <v>0.01739987367573661</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7444825562911378</v>
+        <v>-0.8817880275616937</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8421223274119563</v>
+        <v>-0.9198191215343176</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8856661911223124</v>
+        <v>-0.958865508445934</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.02262317199893232</v>
+        <v>-0.04480442716793716</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3496029593314509</v>
+        <v>-0.4930461744492154</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01315646241192669</v>
+        <v>-0.0002119364838407134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>71.0345320993309</v>
+        <v>49.01463694070916</v>
       </c>
       <c r="B10" t="n">
-        <v>132.0604347922239</v>
+        <v>78.74177626500423</v>
       </c>
       <c r="C10" t="n">
-        <v>46.06598492595418</v>
+        <v>40.00521445962391</v>
       </c>
       <c r="D10" t="n">
-        <v>9.88321486868675</v>
+        <v>8.000284791033373</v>
       </c>
       <c r="E10" t="n">
-        <v>4.807827307679835</v>
+        <v>4.956176258666059</v>
       </c>
       <c r="F10" t="n">
-        <v>6.358073397284218</v>
+        <v>4.315203489954996</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03591037764880782</v>
+        <v>0.1309451169385271</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8156160267954464</v>
+        <v>-0.3810761465316932</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8806813363760955</v>
+        <v>-0.6737683615683033</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9258277491698844</v>
+        <v>-0.6319489742810925</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02535822561617145</v>
+        <v>-0.006495185248862323</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4056329080156887</v>
+        <v>-0.5604260339578246</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01325229708614506</v>
+        <v>-0.001173253415381048</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56.20758122715058</v>
+        <v>89.09952311250474</v>
       </c>
       <c r="B11" t="n">
-        <v>120.4666125839757</v>
+        <v>75.61670729553559</v>
       </c>
       <c r="C11" t="n">
-        <v>46.11896828747586</v>
+        <v>40.00583485248207</v>
       </c>
       <c r="D11" t="n">
-        <v>11.24628717090101</v>
+        <v>9.35601808399913</v>
       </c>
       <c r="E11" t="n">
-        <v>3.915923349800027</v>
+        <v>4.436603828904258</v>
       </c>
       <c r="F11" t="n">
-        <v>4.820990290317709</v>
+        <v>8.997968082549365</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08574804463743885</v>
+        <v>0.01588159638083323</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6335432669889697</v>
+        <v>-0.8905128538161375</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.786986471441103</v>
+        <v>-0.9253009582849158</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8154400546167746</v>
+        <v>-0.962828130127701</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02154877356215433</v>
+        <v>-0.1018095293951416</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2948745511181017</v>
+        <v>-0.5098341021765962</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01652085574345899</v>
+        <v>-0.001312841808465415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>86.74410352769944</v>
+        <v>47.95975191304088</v>
       </c>
       <c r="B12" t="n">
-        <v>113.825901850959</v>
+        <v>75.64395888371739</v>
       </c>
       <c r="C12" t="n">
-        <v>46.06840535279329</v>
+        <v>40.00260449428408</v>
       </c>
       <c r="D12" t="n">
-        <v>8.064873801037505</v>
+        <v>8.15707983256042</v>
       </c>
       <c r="E12" t="n">
-        <v>4.03007318666149</v>
+        <v>4.854289870147634</v>
       </c>
       <c r="F12" t="n">
-        <v>8.375819783245667</v>
+        <v>4.211971385763214</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01763615029267775</v>
+        <v>0.1422750132118246</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8965051460138546</v>
+        <v>-0.3398170823240763</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9292382571189133</v>
+        <v>-0.6554267441137388</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9654645985042081</v>
+        <v>-0.5989683593377055</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.002586028719425911</v>
+        <v>-0.01444547730637413</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5229845020130806</v>
+        <v>-0.5537450954492589</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01340161390697658</v>
+        <v>-0.0005860112139180473</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>53.32868647457737</v>
+        <v>58.17903799089691</v>
       </c>
       <c r="B13" t="n">
-        <v>96.74852653287154</v>
+        <v>59.01978760908388</v>
       </c>
       <c r="C13" t="n">
-        <v>46.11874975567591</v>
+        <v>40.00552451020912</v>
       </c>
       <c r="D13" t="n">
-        <v>6.946087251962001</v>
+        <v>6.862291015895809</v>
       </c>
       <c r="E13" t="n">
-        <v>3.988248745556334</v>
+        <v>4.148237001549992</v>
       </c>
       <c r="F13" t="n">
-        <v>4.699638437512612</v>
+        <v>5.365310388846447</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09700209094581275</v>
+        <v>0.0687747320042784</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5790851659618748</v>
+        <v>-0.6283837268900248</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7637135454761591</v>
+        <v>-0.7868019175314608</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.779238969189062</v>
+        <v>-0.8133345786667204</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.08958037626247936</v>
+        <v>-0.07621635321760535</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6041057836188625</v>
+        <v>-0.447079746193664</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01650737445450138</v>
+        <v>-0.001243014797052411</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>46.00144198681404</v>
+        <v>46.9078264876779</v>
       </c>
       <c r="B14" t="n">
-        <v>111.2996963264361</v>
+        <v>70.83830552734506</v>
       </c>
       <c r="C14" t="n">
-        <v>45.95893260043231</v>
+        <v>40.03888006845304</v>
       </c>
       <c r="D14" t="n">
-        <v>7.860968007878276</v>
+        <v>7.965535343427554</v>
       </c>
       <c r="E14" t="n">
-        <v>4.125815379695276</v>
+        <v>4.356718371974448</v>
       </c>
       <c r="F14" t="n">
-        <v>3.938970427268085</v>
+        <v>4.056705064689831</v>
       </c>
       <c r="G14" t="n">
-        <v>0.170042281081911</v>
+        <v>0.1545686630209444</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3483361108994318</v>
+        <v>-0.2982796030324082</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.65941497372522</v>
+        <v>-0.6379444706277247</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6053637894223605</v>
+        <v>-0.56572667209478</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.08328443821263787</v>
+        <v>-0.009357051976583052</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5554524260616064</v>
+        <v>-0.562718843251186</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.004511104402983247</v>
+        <v>-0.008748015401935094</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>90.30005997859865</v>
+        <v>46.19041169587408</v>
       </c>
       <c r="B15" t="n">
-        <v>110.774959797176</v>
+        <v>75.20570551673761</v>
       </c>
       <c r="C15" t="n">
-        <v>46.17067327782338</v>
+        <v>40.00585671674464</v>
       </c>
       <c r="D15" t="n">
-        <v>7.69839473625999</v>
+        <v>8.31048956197407</v>
       </c>
       <c r="E15" t="n">
-        <v>3.531132578907527</v>
+        <v>4.318009350605146</v>
       </c>
       <c r="F15" t="n">
-        <v>8.90692779899784</v>
+        <v>4.027599627030539</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01536243171929946</v>
+        <v>0.1641905541952416</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9077165019802794</v>
+        <v>-0.261971122124723</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9365181075629337</v>
+        <v>-0.6216243581748182</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9703181698763724</v>
+        <v>-0.5348978310442972</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02309488562554547</v>
+        <v>-0.002428109783035299</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5495477446579288</v>
+        <v>-0.5425392740738693</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0197105513190696</v>
+        <v>-0.001317761267543294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44.24874194970997</v>
+        <v>61.37714527126148</v>
       </c>
       <c r="B16" t="n">
-        <v>103.0003827170753</v>
+        <v>137.6547051339782</v>
       </c>
       <c r="C16" t="n">
-        <v>45.92433763855811</v>
+        <v>40.07824147781938</v>
       </c>
       <c r="D16" t="n">
-        <v>7.83998576091774</v>
+        <v>11.71642713397767</v>
       </c>
       <c r="E16" t="n">
-        <v>4.178788698983293</v>
+        <v>4.58969311588452</v>
       </c>
       <c r="F16" t="n">
-        <v>3.73720904964491</v>
+        <v>5.45223283678593</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1971067936615967</v>
+        <v>0.06064535822467144</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2689590077512689</v>
+        <v>-0.6759314974320405</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6249053350861173</v>
+        <v>-0.8072568744974455</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.540230039924632</v>
+        <v>-0.8434014767901211</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.02879154054039898</v>
+        <v>-0.0008545276557054217</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.543814389179085</v>
+        <v>-0.3123121600577381</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.338596232093522e-05</v>
+        <v>-0.01760433250936139</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45.24283328665418</v>
+        <v>77.35607842056702</v>
       </c>
       <c r="B17" t="n">
-        <v>95.148729455021</v>
+        <v>81.39439251700034</v>
       </c>
       <c r="C17" t="n">
-        <v>45.94809266041378</v>
+        <v>40.01096338631688</v>
       </c>
       <c r="D17" t="n">
-        <v>7.622067336714422</v>
+        <v>10.80195162986425</v>
       </c>
       <c r="E17" t="n">
-        <v>4.564225841773161</v>
+        <v>4.441388247510454</v>
       </c>
       <c r="F17" t="n">
-        <v>3.812842916568137</v>
+        <v>7.390147925423982</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1808762959049728</v>
+        <v>0.02610179293939186</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3156789249987752</v>
+        <v>-0.8369154761282392</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6451323356873923</v>
+        <v>-0.8934928282740457</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5789055307722287</v>
+        <v>-0.9371866021214365</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.002415305681175986</v>
+        <v>-0.1499168809936915</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.550415217272332</v>
+        <v>-0.4406663234503962</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0032453738297555</v>
+        <v>-0.00246676192129841</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>76.38200252131813</v>
+        <v>54.81296015280036</v>
       </c>
       <c r="B18" t="n">
-        <v>116.9566810433298</v>
+        <v>93.9432171039297</v>
       </c>
       <c r="C18" t="n">
-        <v>46.0963011989612</v>
+        <v>40.02225917427419</v>
       </c>
       <c r="D18" t="n">
-        <v>9.220628819403819</v>
+        <v>7.49957364827298</v>
       </c>
       <c r="E18" t="n">
-        <v>4.56975749817199</v>
+        <v>4.577070163464827</v>
       </c>
       <c r="F18" t="n">
-        <v>6.986818413591883</v>
+        <v>4.991123555482662</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02761321102286679</v>
+        <v>0.08596351748307159</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8506970291852209</v>
+        <v>-0.5552486248786588</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.900996029178032</v>
+        <v>-0.7527719300189915</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9439211631775577</v>
+        <v>-0.7627493962859802</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.00245606630594758</v>
+        <v>-0.06342897438301236</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.445578884946727</v>
+        <v>-0.5971487476344022</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0151225165993796</v>
+        <v>-0.005008314211692177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>59.35661668885135</v>
+        <v>73.18711076153217</v>
       </c>
       <c r="B19" t="n">
-        <v>107.2043571132861</v>
+        <v>170.5201817643879</v>
       </c>
       <c r="C19" t="n">
-        <v>46.33756926729271</v>
+        <v>40.00549712901534</v>
       </c>
       <c r="D19" t="n">
-        <v>10.89012941784305</v>
+        <v>11.11607198390744</v>
       </c>
       <c r="E19" t="n">
-        <v>3.563370373911605</v>
+        <v>4.159620698510318</v>
       </c>
       <c r="F19" t="n">
-        <v>5.178524789898396</v>
+        <v>6.8492950842681</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06953639775688986</v>
+        <v>0.03183695270485298</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6882123574907538</v>
+        <v>-0.8064407120548753</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8136050592685046</v>
+        <v>-0.8753380951545614</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8511314710839351</v>
+        <v>-0.9209584601508761</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06213987102919345</v>
+        <v>-0.09077525482230921</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3402423048355841</v>
+        <v>-0.3964581641759166</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.02552890019045554</v>
+        <v>-0.001236854028451584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>64.98492843766083</v>
+        <v>71.84787464031676</v>
       </c>
       <c r="B20" t="n">
-        <v>101.3977468986314</v>
+        <v>136.3474964819458</v>
       </c>
       <c r="C20" t="n">
-        <v>45.93394097001963</v>
+        <v>40.55042856132228</v>
       </c>
       <c r="D20" t="n">
-        <v>10.43653558386141</v>
+        <v>10.87932816227899</v>
       </c>
       <c r="E20" t="n">
-        <v>3.966680941313116</v>
+        <v>4.2435492737552</v>
       </c>
       <c r="F20" t="n">
-        <v>5.715506780918046</v>
+        <v>6.651884487116633</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04968447556223224</v>
+        <v>0.03399468391475541</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7609632478836691</v>
+        <v>-0.7957885468598843</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8508320195478479</v>
+        <v>-0.8694479995670131</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8953634497273946</v>
+        <v>-0.9151478920010114</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.04293247022833128</v>
+        <v>-0.03985928090630893</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3712131520857971</v>
+        <v>-0.386916106812257</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.001439511152171991</v>
+        <v>-0.1238464262975128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>69.53029826987905</v>
+        <v>93.43812112773183</v>
       </c>
       <c r="B21" t="n">
-        <v>107.0662364225541</v>
+        <v>77.10733037608048</v>
       </c>
       <c r="C21" t="n">
-        <v>46.06598492595418</v>
+        <v>40.00478929830106</v>
       </c>
       <c r="D21" t="n">
-        <v>10.25431300902228</v>
+        <v>8.361577247970573</v>
       </c>
       <c r="E21" t="n">
-        <v>3.817432028555761</v>
+        <v>4.657507360655559</v>
       </c>
       <c r="F21" t="n">
-        <v>6.221734709215759</v>
+        <v>9.583212082711933</v>
       </c>
       <c r="G21" t="n">
-        <v>0.03888497964680263</v>
+        <v>0.01347448533859344</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8036725547179802</v>
+        <v>-0.9045000941032902</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8739530954236563</v>
+        <v>-0.9343550295912242</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9193845281154718</v>
+        <v>-0.9689755375279754</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.06687506499131406</v>
+        <v>-0.006935415777238781</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3943961764195482</v>
+        <v>-0.5407466130350893</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.01325229708614506</v>
+        <v>-0.00107759211773778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>92.22455429460743</v>
+        <v>94.80790783690702</v>
       </c>
       <c r="B22" t="n">
-        <v>95.85403814334111</v>
+        <v>89.9361786117292</v>
       </c>
       <c r="C22" t="n">
-        <v>45.92809511406413</v>
+        <v>40.02789607443822</v>
       </c>
       <c r="D22" t="n">
-        <v>7.545312815691734</v>
+        <v>8.359040839733058</v>
       </c>
       <c r="E22" t="n">
-        <v>3.995932163832665</v>
+        <v>4.126632535158729</v>
       </c>
       <c r="F22" t="n">
-        <v>9.203559555128008</v>
+        <v>9.826607805700796</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01429816716091255</v>
+        <v>0.01283636513585735</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9130881499541798</v>
+        <v>-0.9083652281989445</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9400674229260588</v>
+        <v>-0.9368810533443449</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.972577602879768</v>
+        <v>-0.9706216261794816</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.04298758993815657</v>
+        <v>-0.04828022484649368</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5639238513933883</v>
+        <v>-0.5505063433379626</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0005957322793270288</v>
+        <v>-0.00627661674859864</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>46.89718472931128</v>
+        <v>81.95625415125802</v>
       </c>
       <c r="B23" t="n">
-        <v>115.6499196556621</v>
+        <v>75.66357392353981</v>
       </c>
       <c r="C23" t="n">
-        <v>45.92482124996521</v>
+        <v>45.69549967766393</v>
       </c>
       <c r="D23" t="n">
-        <v>7.870707272170336</v>
+        <v>9.609758163610989</v>
       </c>
       <c r="E23" t="n">
-        <v>4.079247629492129</v>
+        <v>4.511678457113081</v>
       </c>
       <c r="F23" t="n">
-        <v>4.019216918909153</v>
+        <v>7.911302591742167</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1582368521105055</v>
+        <v>0.02120138290886502</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3842968823413532</v>
+        <v>-0.862038944379129</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6753669033301857</v>
+        <v>-0.9083259823244327</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6340118155156262</v>
+        <v>-0.9496636391420693</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.06187595752316903</v>
+        <v>-0.1540430522980786</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5502355279629637</v>
+        <v>-0.4743051084810743</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0001231894421004788</v>
+        <v>-0.01611421203747007</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>42.13546602576132</v>
+        <v>62.47649602956979</v>
       </c>
       <c r="B24" t="n">
-        <v>102.6247697160593</v>
+        <v>124.3895121589937</v>
       </c>
       <c r="C24" t="n">
-        <v>45.93134692553096</v>
+        <v>40.08164979996714</v>
       </c>
       <c r="D24" t="n">
-        <v>7.994785031866663</v>
+        <v>11.72422690048451</v>
       </c>
       <c r="E24" t="n">
-        <v>4.288292319232629</v>
+        <v>4.086225356228848</v>
       </c>
       <c r="F24" t="n">
-        <v>3.535256610625118</v>
+        <v>5.581987160345852</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2378914554830153</v>
+        <v>0.05680276452424602</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1546976477103829</v>
+        <v>-0.6923819135897468</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5768635622412251</v>
+        <v>-0.8153758379610692</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.442273643022749</v>
+        <v>-0.8538622506222462</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.009414975844069813</v>
+        <v>-0.01918754583390599</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5297821060586401</v>
+        <v>-0.3201450342106846</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.001065092084815723</v>
+        <v>-0.01837120499260686</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>52.38800922179655</v>
+        <v>45.67139429785415</v>
       </c>
       <c r="B25" t="n">
-        <v>103.1858394036089</v>
+        <v>75.08558081087421</v>
       </c>
       <c r="C25" t="n">
-        <v>46.46600419499165</v>
+        <v>40.00325460178607</v>
       </c>
       <c r="D25" t="n">
-        <v>7.019515890530008</v>
+        <v>8.274271652609539</v>
       </c>
       <c r="E25" t="n">
-        <v>4.844853487188039</v>
+        <v>4.352403288361867</v>
       </c>
       <c r="F25" t="n">
-        <v>4.596533667106407</v>
+        <v>3.961730482286647</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1037311290049802</v>
+        <v>0.1713547631921331</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5563912030994078</v>
+        <v>-0.2403432619680013</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7534651803939153</v>
+        <v>-0.6130925931043385</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7632904922549112</v>
+        <v>-0.5173966133814434</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.08278039723601682</v>
+        <v>-0.01234859733088443</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5978596283551812</v>
+        <v>-0.5468640629360519</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0299288273088163</v>
+        <v>-0.0007322854018657066</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>47.63930061333432</v>
+        <v>49.5789259313547</v>
       </c>
       <c r="B26" t="n">
-        <v>110.774959797176</v>
+        <v>79.85251983603938</v>
       </c>
       <c r="C26" t="n">
-        <v>46.11874975567591</v>
+        <v>40.18671743483348</v>
       </c>
       <c r="D26" t="n">
-        <v>7.397504036995773</v>
+        <v>7.917080098971875</v>
       </c>
       <c r="E26" t="n">
-        <v>4.174712081622427</v>
+        <v>4.433989080737511</v>
       </c>
       <c r="F26" t="n">
-        <v>4.057936427050382</v>
+        <v>4.37745564797796</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1485410635809105</v>
+        <v>0.1253871949081948</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4126815943625994</v>
+        <v>-0.4017012380534744</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6882667043675459</v>
+        <v>-0.6830484301894195</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6563403083268454</v>
+        <v>-0.648162052520444</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0196878196752832</v>
+        <v>-0.006905478084572828</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5663279088597315</v>
+        <v>-0.5639998642319131</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.01650737445450138</v>
+        <v>-0.04201142283753484</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96.48929350818828</v>
+        <v>44.78524966846216</v>
       </c>
       <c r="B27" t="n">
-        <v>89.56573105476531</v>
+        <v>75.75160953544056</v>
       </c>
       <c r="C27" t="n">
-        <v>45.94446761402018</v>
+        <v>40.00485727492823</v>
       </c>
       <c r="D27" t="n">
-        <v>7.20950618884125</v>
+        <v>8.334522873195166</v>
       </c>
       <c r="E27" t="n">
-        <v>4.569954104036704</v>
+        <v>4.648943871962611</v>
       </c>
       <c r="F27" t="n">
-        <v>9.901472705461526</v>
+        <v>3.870816974210974</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0122830820423215</v>
+        <v>0.184682193766705</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9235240083057743</v>
+        <v>-0.1948972662431802</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9470800906849545</v>
+        <v>-0.5939643619598428</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.97683588960893</v>
+        <v>-0.4786342586269366</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1104238372576863</v>
+        <v>-0.002015386996780257</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5957817506988482</v>
+        <v>-0.541104122845004</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.002822093623231549</v>
+        <v>-0.001092886858851394</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67.56412713009404</v>
+        <v>45.2868863066893</v>
       </c>
       <c r="B28" t="n">
-        <v>107.020815732575</v>
+        <v>75.74971227982675</v>
       </c>
       <c r="C28" t="n">
-        <v>46.32038071054042</v>
+        <v>40.02603637070456</v>
       </c>
       <c r="D28" t="n">
-        <v>10.20510533506175</v>
+        <v>8.407153361794053</v>
       </c>
       <c r="E28" t="n">
-        <v>3.988032801137292</v>
+        <v>4.648943871962611</v>
       </c>
       <c r="F28" t="n">
-        <v>5.970737508067038</v>
+        <v>3.940084908485089</v>
       </c>
       <c r="G28" t="n">
-        <v>0.04314238523545495</v>
+        <v>0.177095968400964</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7865809134478919</v>
+        <v>-0.2173868152350555</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8645612004471823</v>
+        <v>-0.6026829854023492</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9099563136946471</v>
+        <v>-0.4971584562686206</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.02677683763916623</v>
+        <v>-0.001702060857952372</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.3797087409043577</v>
+        <v>-0.5368169466090322</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02494005416286148</v>
+        <v>-0.005858183408526119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>81.76170559402489</v>
+        <v>84.59982213127105</v>
       </c>
       <c r="B29" t="n">
-        <v>107.020815732575</v>
+        <v>75.66682829958962</v>
       </c>
       <c r="C29" t="n">
-        <v>46.32038071054042</v>
+        <v>40.00687351512222</v>
       </c>
       <c r="D29" t="n">
-        <v>10.20510533506175</v>
+        <v>9.855258768153416</v>
       </c>
       <c r="E29" t="n">
-        <v>3.984021127167358</v>
+        <v>4.547672098568784</v>
       </c>
       <c r="F29" t="n">
-        <v>7.954188558188793</v>
+        <v>8.342262287299064</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02187551621550828</v>
+        <v>0.01900601967204081</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8770745632637171</v>
+        <v>-0.8729076653604781</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9168366279976051</v>
+        <v>-0.9142824791730048</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9566172449892479</v>
+        <v>-0.9547248035034525</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.2881789560748975</v>
+        <v>-0.09243035442929694</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.4857656420262207</v>
+        <v>-0.4777737326853062</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.02494005416286148</v>
+        <v>-0.001546540902499782</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>77.4772181461167</v>
+        <v>51.29827073209034</v>
       </c>
       <c r="B30" t="n">
-        <v>91.02233123275734</v>
+        <v>78.20847084607747</v>
       </c>
       <c r="C30" t="n">
-        <v>45.93137948736914</v>
+        <v>40.44366211886538</v>
       </c>
       <c r="D30" t="n">
-        <v>10.25424718507721</v>
+        <v>7.914815920491125</v>
       </c>
       <c r="E30" t="n">
-        <v>3.445309820440646</v>
+        <v>4.427336431315727</v>
       </c>
       <c r="F30" t="n">
-        <v>7.309735956950289</v>
+        <v>4.603278006118584</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02641618264102457</v>
+        <v>0.1103458520833488</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8564940179792884</v>
+        <v>-0.4589815768284677</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.9043350921373704</v>
+        <v>-0.7092335521874215</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.946762351702234</v>
+        <v>-0.6921873082348959</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.210305467110042</v>
+        <v>-0.06355719793159986</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4537602220332924</v>
+        <v>-0.5748890479699054</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.001069791993832805</v>
+        <v>-0.09982397674471094</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>61.04610263118246</v>
+        <v>56.72983462666254</v>
       </c>
       <c r="B31" t="n">
-        <v>110.9300515325838</v>
+        <v>99.89393251042233</v>
       </c>
       <c r="C31" t="n">
-        <v>45.94414608894022</v>
+        <v>40.00497031456176</v>
       </c>
       <c r="D31" t="n">
-        <v>10.98980630540908</v>
+        <v>7.596922037248391</v>
       </c>
       <c r="E31" t="n">
-        <v>4.574632064737376</v>
+        <v>4.474397906282445</v>
       </c>
       <c r="F31" t="n">
-        <v>5.30231783273942</v>
+        <v>5.275056848481713</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0629006320742935</v>
+        <v>0.07572483803508058</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7126052304507843</v>
+        <v>-0.5979883025509822</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8257162734565896</v>
+        <v>-0.7721442445622742</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8663460099211819</v>
+        <v>-0.7925197840755025</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.0492154521069232</v>
+        <v>-0.14915498295019</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3310186433960288</v>
+        <v>-0.6092889526355294</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.00278455059964757</v>
+        <v>-0.001118320776395676</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>57.16283280723027</v>
+        <v>56.12095766299139</v>
       </c>
       <c r="B32" t="n">
-        <v>110.9187836200533</v>
+        <v>99.86955361965032</v>
       </c>
       <c r="C32" t="n">
-        <v>46.18280242041417</v>
+        <v>40.13088200641246</v>
       </c>
       <c r="D32" t="n">
-        <v>11.2466397758761</v>
+        <v>7.46050911884074</v>
       </c>
       <c r="E32" t="n">
-        <v>3.919236808472216</v>
+        <v>4.646949790860135</v>
       </c>
       <c r="F32" t="n">
-        <v>4.987625349165159</v>
+        <v>5.170413282199327</v>
       </c>
       <c r="G32" t="n">
-        <v>0.08021063151150559</v>
+        <v>0.07876433636380664</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6515460770569209</v>
+        <v>-0.5850761453407198</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7956682152191435</v>
+        <v>-0.7662472406893622</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8274295318182169</v>
+        <v>-0.7836367620041389</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.08441819712470762</v>
+        <v>-0.1000980369595664</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.3239712212356082</v>
+        <v>-0.6054327318656121</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.02022689349489178</v>
+        <v>-0.02944845144280311</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>43.35966353582257</v>
+        <v>98.80103071715217</v>
       </c>
       <c r="B33" t="n">
-        <v>95.9571953930453</v>
+        <v>85.87332099933326</v>
       </c>
       <c r="C33" t="n">
-        <v>46.86675691051478</v>
+        <v>40.06041487335896</v>
       </c>
       <c r="D33" t="n">
-        <v>7.926459695542158</v>
+        <v>7.860618434641267</v>
       </c>
       <c r="E33" t="n">
-        <v>4.589781409654237</v>
+        <v>4.940504669815982</v>
       </c>
       <c r="F33" t="n">
-        <v>3.681193242594135</v>
+        <v>10.47547593731151</v>
       </c>
       <c r="G33" t="n">
-        <v>0.213319317371227</v>
+        <v>0.01117975364417167</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.223406560516851</v>
+        <v>-0.918505680202814</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6054953075336231</v>
+        <v>-0.9436403810325408</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5017079315263592</v>
+        <v>-0.9748354538357497</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.04500358186879579</v>
+        <v>-0.06107810345516568</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5379108534038639</v>
+        <v>-0.5789573438597092</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.03886563375087086</v>
+        <v>-0.01359334650576499</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>58.03106846414819</v>
+        <v>50.71778761792601</v>
       </c>
       <c r="B34" t="n">
-        <v>120.4666125839757</v>
+        <v>78.88412913392077</v>
       </c>
       <c r="C34" t="n">
-        <v>46.08467194628597</v>
+        <v>40.9011584634774</v>
       </c>
       <c r="D34" t="n">
-        <v>11.40886049826981</v>
+        <v>7.916273580580424</v>
       </c>
       <c r="E34" t="n">
-        <v>3.975555947010945</v>
+        <v>4.025354008091939</v>
       </c>
       <c r="F34" t="n">
-        <v>5.041436422063195</v>
+        <v>4.543768227899716</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07619886188307921</v>
+        <v>0.115213867479757</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6662776794311697</v>
+        <v>-0.4404337128826307</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8026721531370437</v>
+        <v>-0.700664641403953</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8369865824682454</v>
+        <v>-0.678079814004574</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.07551897049990478</v>
+        <v>-0.05729758391385082</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.3084961279301301</v>
+        <v>-0.5712126549135315</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.01440510469084741</v>
+        <v>-0.2027606542824148</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>80.91007355431914</v>
+        <v>74.57037097372967</v>
       </c>
       <c r="B35" t="n">
-        <v>105.0055064053982</v>
+        <v>99.96726856156035</v>
       </c>
       <c r="C35" t="n">
-        <v>45.92775419416417</v>
+        <v>40.06525756292022</v>
       </c>
       <c r="D35" t="n">
-        <v>9.117652420779597</v>
+        <v>11.45910342545669</v>
       </c>
       <c r="E35" t="n">
-        <v>4.010537135183812</v>
+        <v>4.171753161620924</v>
       </c>
       <c r="F35" t="n">
-        <v>7.630555370501503</v>
+        <v>7.10027751108312</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02254393615496698</v>
+        <v>0.02984432043599895</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8735269372627099</v>
+        <v>-0.816584714918403</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9147588377911717</v>
+        <v>-0.8809863617125996</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9549737711889078</v>
+        <v>-0.9263868154158132</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.08136273035347324</v>
+        <v>-0.1678159637530491</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.4794038913053675</v>
+        <v>-0.4063138931878238</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0005465245993720687</v>
+        <v>-0.01468295165705041</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>40.68656030505583</v>
+        <v>52.03537689411544</v>
       </c>
       <c r="B36" t="n">
-        <v>89.23012519598996</v>
+        <v>75.27883652823556</v>
       </c>
       <c r="C36" t="n">
-        <v>45.93142632989768</v>
+        <v>40.00516214943652</v>
       </c>
       <c r="D36" t="n">
-        <v>8.152909314824671</v>
+        <v>7.833350045153796</v>
       </c>
       <c r="E36" t="n">
-        <v>3.432061240174823</v>
+        <v>4.469106184842049</v>
       </c>
       <c r="F36" t="n">
-        <v>3.41168686576486</v>
+        <v>4.671738078981591</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2723671425056127</v>
+        <v>0.104515213499957</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0620299720609464</v>
+        <v>-0.4813879720126414</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.539150066138872</v>
+        <v>-0.7196914765162545</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3594860381670764</v>
+        <v>-0.7090215446851027</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0100134277358693</v>
+        <v>-0.05613962928199346</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5201612822668361</v>
+        <v>-0.5795573869960644</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.001076553148440561</v>
+        <v>-0.00116148362321572</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>97.29011378888862</v>
+        <v>54.36264288330034</v>
       </c>
       <c r="B37" t="n">
-        <v>89.13518653190806</v>
+        <v>78.77982380253282</v>
       </c>
       <c r="C37" t="n">
-        <v>45.9449111252344</v>
+        <v>40.9011584634774</v>
       </c>
       <c r="D37" t="n">
-        <v>7.197221844093582</v>
+        <v>7.237908640182292</v>
       </c>
       <c r="E37" t="n">
-        <v>4.564225841773161</v>
+        <v>4.183429930765564</v>
       </c>
       <c r="F37" t="n">
-        <v>10.04463717328646</v>
+        <v>4.912692999288945</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0119517335305866</v>
+        <v>0.08859323168768556</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9252819364340618</v>
+        <v>-0.5443638427236658</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9482755252372035</v>
+        <v>-0.7479314945631831</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9775351510072812</v>
+        <v>-0.7550184581253599</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1371888043259367</v>
+        <v>-0.0002864356385263009</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6017639340368302</v>
+        <v>-0.5942967382609021</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.002873880413790426</v>
+        <v>-0.2027606542824148</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>94.34627161740431</v>
+        <v>78.64217036546844</v>
       </c>
       <c r="B38" t="n">
-        <v>110.774959797176</v>
+        <v>93.71684598740941</v>
       </c>
       <c r="C38" t="n">
-        <v>46.11854055876172</v>
+        <v>40.00549712901534</v>
       </c>
       <c r="D38" t="n">
-        <v>7.403900920042894</v>
+        <v>11.21636421323401</v>
       </c>
       <c r="E38" t="n">
-        <v>4.126793376896154</v>
+        <v>4.432193156634041</v>
       </c>
       <c r="F38" t="n">
-        <v>9.555615816333324</v>
+        <v>7.646140374060138</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01324543299705754</v>
+        <v>0.02468545705185451</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9185084212109464</v>
+        <v>-0.8428343999650855</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.943685557502283</v>
+        <v>-0.8961186967207048</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9748110422934464</v>
+        <v>-0.9400077266238337</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.08454626368302519</v>
+        <v>-0.198725204508295</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5797732277419033</v>
+        <v>-0.4353254638539626</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.01649446903730397</v>
+        <v>-0.001236854028451584</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>66.1150423948699</v>
+        <v>75.46762009791709</v>
       </c>
       <c r="B39" t="n">
-        <v>100.7326495031341</v>
+        <v>89.74792494482385</v>
       </c>
       <c r="C39" t="n">
-        <v>40.48479635377174</v>
+        <v>40.00549712901534</v>
       </c>
       <c r="D39" t="n">
-        <v>10.82172764382331</v>
+        <v>11.21636421323401</v>
       </c>
       <c r="E39" t="n">
-        <v>4.298225554293476</v>
+        <v>4.252550429299833</v>
       </c>
       <c r="F39" t="n">
-        <v>5.916675740459937</v>
+        <v>7.185052643723031</v>
       </c>
       <c r="G39" t="n">
-        <v>0.04677545648919598</v>
+        <v>0.02855695531136747</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7725510480789157</v>
+        <v>-0.8229129889028004</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.856942032462893</v>
+        <v>-0.8846101059144216</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9020173798798907</v>
+        <v>-0.9297392753778893</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.01166582088273563</v>
+        <v>-0.1453076589136556</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.3796251177153684</v>
+        <v>-0.4127067931976593</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.06071185329840381</v>
+        <v>-0.001236854028451584</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>45.35448758348109</v>
+        <v>96.18496015187539</v>
       </c>
       <c r="B40" t="n">
-        <v>95.68910902326837</v>
+        <v>76.60018873245647</v>
       </c>
       <c r="C40" t="n">
-        <v>45.92596053384904</v>
+        <v>40.02847161888955</v>
       </c>
       <c r="D40" t="n">
-        <v>7.997064153661398</v>
+        <v>8.609599753754592</v>
       </c>
       <c r="E40" t="n">
-        <v>3.286738217877017</v>
+        <v>4.288131601793383</v>
       </c>
       <c r="F40" t="n">
-        <v>3.88679024118205</v>
+        <v>10.11512514516563</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1795904576114908</v>
+        <v>0.01224779139881066</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.3203362276759814</v>
+        <v>-0.9120104327330828</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6470986175505236</v>
+        <v>-0.9392671006877934</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5826489869071448</v>
+        <v>-0.972151579467894</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.09618872739765798</v>
+        <v>-0.1420061078252067</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5511566087238382</v>
+        <v>-0.560317841082112</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0002876313439647782</v>
+        <v>-0.006406114250149531</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40.89837109306426</v>
+        <v>69.9685509490894</v>
       </c>
       <c r="B41" t="n">
-        <v>107.9249131999428</v>
+        <v>169.8523116134383</v>
       </c>
       <c r="C41" t="n">
-        <v>45.92545537404761</v>
+        <v>40.00318779405403</v>
       </c>
       <c r="D41" t="n">
-        <v>8.134954538876816</v>
+        <v>11.05118998117754</v>
       </c>
       <c r="E41" t="n">
-        <v>3.555621422036586</v>
+        <v>4.13494652018669</v>
       </c>
       <c r="F41" t="n">
-        <v>3.430102403110407</v>
+        <v>6.404427982488642</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2669519966794652</v>
+        <v>0.03740050658799999</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.07639738778267165</v>
+        <v>-0.7793909709458027</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5449286581027877</v>
+        <v>-0.860503498069826</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3725064658004903</v>
+        <v>-0.9060020215291337</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.01100893998341441</v>
+        <v>-0.02422850556470747</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.5215677190277043</v>
+        <v>-0.373525925512262</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0002147176130919174</v>
+        <v>-0.000717253662156081</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42.01925446742442</v>
+        <v>96.94034791017533</v>
       </c>
       <c r="B42" t="n">
-        <v>107.4413639739928</v>
+        <v>89.9361786117292</v>
       </c>
       <c r="C42" t="n">
-        <v>45.95599092005703</v>
+        <v>40.02789607443822</v>
       </c>
       <c r="D42" t="n">
-        <v>8.002618357558001</v>
+        <v>8.359040839733058</v>
       </c>
       <c r="E42" t="n">
-        <v>3.809507903856097</v>
+        <v>4.126632535158729</v>
       </c>
       <c r="F42" t="n">
-        <v>3.52506037796822</v>
+        <v>10.21197912052539</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2404416053042947</v>
+        <v>0.01192349860107524</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1477322660800376</v>
+        <v>-0.9139616453291117</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5739918774881941</v>
+        <v>-0.9405766661472262</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4361514623276244</v>
+        <v>-0.9729651974497154</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.008765430498708581</v>
+        <v>-0.1126878468650922</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5290104541082387</v>
+        <v>-0.5656999788599992</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.004167617743343391</v>
+        <v>-0.00627661674859864</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>41.51195308433076</v>
+        <v>43.08457620153614</v>
       </c>
       <c r="B43" t="n">
-        <v>115.3067466953953</v>
+        <v>75.65409558486132</v>
       </c>
       <c r="C43" t="n">
-        <v>45.92778026943845</v>
+        <v>40.00493990829203</v>
       </c>
       <c r="D43" t="n">
-        <v>8.054771680795699</v>
+        <v>8.441259409164072</v>
       </c>
       <c r="E43" t="n">
-        <v>3.703683929229101</v>
+        <v>4.807117777741808</v>
       </c>
       <c r="F43" t="n">
-        <v>3.480002796679407</v>
+        <v>3.700324037599939</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2519842873906386</v>
+        <v>0.2142224230736885</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1164117305005192</v>
+        <v>-0.09687977305267514</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5611564982398193</v>
+        <v>-0.5536519677648005</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4084194033288401</v>
+        <v>-0.3925718350980033</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.007529357066431915</v>
+        <v>-0.01094185257359272</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5256419414808565</v>
+        <v>-0.5372305080102409</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.0005502882510448541</v>
+        <v>-0.001111479365706602</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>93.75968837500633</v>
+        <v>80.3649454762775</v>
       </c>
       <c r="B44" t="n">
-        <v>110.774959797176</v>
+        <v>85.25068632667924</v>
       </c>
       <c r="C44" t="n">
-        <v>46.17067327782338</v>
+        <v>40.00548755233068</v>
       </c>
       <c r="D44" t="n">
-        <v>7.69839473625999</v>
+        <v>9.955961182043509</v>
       </c>
       <c r="E44" t="n">
-        <v>4.125815379695276</v>
+        <v>4.827857130517824</v>
       </c>
       <c r="F44" t="n">
-        <v>9.502672984295719</v>
+        <v>7.700102878909931</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01354081699942244</v>
+        <v>0.02272305674282231</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.917033235435045</v>
+        <v>-0.8526400631031145</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.942679917118825</v>
+        <v>-0.9020390186485275</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9742058652757387</v>
+        <v>-0.9449372539920072</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.1350955794241337</v>
+        <v>-0.02027715658999795</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5753914100187759</v>
+        <v>-0.4476002365184771</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0197105513190696</v>
+        <v>-0.001234699274401951</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>40.28619410368059</v>
+        <v>90.88401078613336</v>
       </c>
       <c r="B45" t="n">
-        <v>83.83204468673188</v>
+        <v>75.61481003992176</v>
       </c>
       <c r="C45" t="n">
-        <v>45.93637254826311</v>
+        <v>40.0270139482584</v>
       </c>
       <c r="D45" t="n">
-        <v>8.161855818903097</v>
+        <v>9.428648572598018</v>
       </c>
       <c r="E45" t="n">
-        <v>2.945314500245428</v>
+        <v>4.436603828904258</v>
       </c>
       <c r="F45" t="n">
-        <v>3.388458834554022</v>
+        <v>9.313248191971898</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2827025360108134</v>
+        <v>0.01485528049343448</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.03423776705684366</v>
+        <v>-0.8965280703102524</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5280697988965783</v>
+        <v>-0.9291283337075208</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.3341613815601952</v>
+        <v>-0.9655003686934399</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.02547337227198377</v>
+        <v>-0.1584312349307013</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5232169588501715</v>
+        <v>-0.5225485768512002</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.001790480174525028</v>
+        <v>-0.006078138358140139</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>98.57521558866688</v>
+        <v>43.59768249359028</v>
       </c>
       <c r="B46" t="n">
-        <v>89.56573105476531</v>
+        <v>75.66422400670601</v>
       </c>
       <c r="C46" t="n">
-        <v>46.06475297021191</v>
+        <v>40.01107180862959</v>
       </c>
       <c r="D46" t="n">
-        <v>7.401706043637429</v>
+        <v>8.351099417755105</v>
       </c>
       <c r="E46" t="n">
-        <v>4.31161467034144</v>
+        <v>4.438644736594378</v>
       </c>
       <c r="F46" t="n">
-        <v>10.31710163377933</v>
+        <v>3.741815421460303</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01145578958184012</v>
+        <v>0.2046364967537151</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.9279690846610271</v>
+        <v>-0.1281099879012295</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9501003151203858</v>
+        <v>-0.5663712232140576</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9785924710540607</v>
+        <v>-0.4203561014603604</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.2313198315008008</v>
+        <v>-0.004195746838317214</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.6113637340912456</v>
+        <v>-0.5406512166239352</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.01317629738565126</v>
+        <v>-0.002491156941657746</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>77.01379084116036</v>
+        <v>47.47852186779017</v>
       </c>
       <c r="B47" t="n">
-        <v>90.96211246401312</v>
+        <v>70.77965291161522</v>
       </c>
       <c r="C47" t="n">
-        <v>46.4931155359439</v>
+        <v>40.03888006845304</v>
       </c>
       <c r="D47" t="n">
-        <v>10.26950423493503</v>
+        <v>8.02940336667117</v>
       </c>
       <c r="E47" t="n">
-        <v>3.992225580562764</v>
+        <v>4.503030086248724</v>
       </c>
       <c r="F47" t="n">
-        <v>7.26602042755622</v>
+        <v>4.134751568552923</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02700439449012254</v>
+        <v>0.1477056123909784</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8539592269418425</v>
+        <v>-0.3229131157534028</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.9028088792729715</v>
+        <v>-0.6486494153479733</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9455116853491886</v>
+        <v>-0.5858624665813448</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.213668012508054</v>
+        <v>-0.0425021452034123</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.4502983877505101</v>
+        <v>-0.5665234791186011</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.03085760833752894</v>
+        <v>-0.008748015401935094</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41.54535663249307</v>
+        <v>70.20465410576399</v>
       </c>
       <c r="B48" t="n">
-        <v>109.8412703800055</v>
+        <v>169.8523116134383</v>
       </c>
       <c r="C48" t="n">
-        <v>45.92778026943845</v>
+        <v>40.00549712901534</v>
       </c>
       <c r="D48" t="n">
-        <v>8.054771680795699</v>
+        <v>11.05118998117754</v>
       </c>
       <c r="E48" t="n">
-        <v>3.514969418251725</v>
+        <v>4.13494652018669</v>
       </c>
       <c r="F48" t="n">
-        <v>3.483463636197141</v>
+        <v>6.435722961648318</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2512077310352528</v>
+        <v>0.0369491942671893</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1185175848265474</v>
+        <v>-0.7815462817832473</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5620149837867685</v>
+        <v>-0.8616690989252057</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.410293603896391</v>
+        <v>-0.9072172027992554</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.008412470275787615</v>
+        <v>-0.02837861939160059</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5258637431110788</v>
+        <v>-0.3752081605035684</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0005502882510448541</v>
+        <v>-0.001236854028451584</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>81.06195057051731</v>
+        <v>90.83191718738982</v>
       </c>
       <c r="B49" t="n">
-        <v>105.1020094617599</v>
+        <v>87.91915076982181</v>
       </c>
       <c r="C49" t="n">
-        <v>45.92775419416417</v>
+        <v>40.00687818576853</v>
       </c>
       <c r="D49" t="n">
-        <v>9.171797030869506</v>
+        <v>9.103005323011997</v>
       </c>
       <c r="E49" t="n">
-        <v>4.322424867285248</v>
+        <v>4.642442751712577</v>
       </c>
       <c r="F49" t="n">
-        <v>7.662513063090889</v>
+        <v>9.250794291600783</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0224038105748746</v>
+        <v>0.01486303153143778</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8741965966448308</v>
+        <v>-0.8964006511374933</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9151650399074323</v>
+        <v>-0.9290714504679394</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9552877649693567</v>
+        <v>-0.9654478792251197</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.0956420421284921</v>
+        <v>-0.09547649054450254</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.4805384232067432</v>
+        <v>-0.5221774099601524</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0005465245993720687</v>
+        <v>-0.001547591797919357</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>84.10646408853304</v>
+        <v>52.03537689411544</v>
       </c>
       <c r="B50" t="n">
-        <v>107.020815732575</v>
+        <v>101.0620917983871</v>
       </c>
       <c r="C50" t="n">
-        <v>41.57415143315028</v>
+        <v>40.00516214943652</v>
       </c>
       <c r="D50" t="n">
-        <v>10.20510533506175</v>
+        <v>7.833350045153796</v>
       </c>
       <c r="E50" t="n">
-        <v>4.151350722362436</v>
+        <v>4.47657285387893</v>
       </c>
       <c r="F50" t="n">
-        <v>8.334582869146363</v>
+        <v>4.671738078981591</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01983907428877256</v>
+        <v>0.104515213499957</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.886629272694066</v>
+        <v>-0.4813879720126414</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9227879746301818</v>
+        <v>-0.7196914765162545</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9610160922385295</v>
+        <v>-0.7090215446851027</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.255355310556487</v>
+        <v>-0.05613962928199346</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.5032811514800667</v>
+        <v>-0.5795573869960644</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.08983700880767169</v>
+        <v>-0.00116148362321572</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>43.64036176049146</v>
+        <v>43.60862368986148</v>
       </c>
       <c r="B51" t="n">
-        <v>110.9893438431885</v>
+        <v>75.08558081087421</v>
       </c>
       <c r="C51" t="n">
-        <v>46.86698577708343</v>
+        <v>40.0112371799776</v>
       </c>
       <c r="D51" t="n">
-        <v>7.926459695542158</v>
+        <v>8.351099417755105</v>
       </c>
       <c r="E51" t="n">
-        <v>4.589781409654237</v>
+        <v>4.438644736594378</v>
       </c>
       <c r="F51" t="n">
-        <v>3.71166258250686</v>
+        <v>3.74302002397676</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2081236107428077</v>
+        <v>0.204440549387827</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2381139038360696</v>
+        <v>-0.1287585842737053</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6117137116426189</v>
+        <v>-0.5666363978205979</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.5142145765675568</v>
+        <v>-0.4209293721454574</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.05251771942786173</v>
+        <v>-0.004509801521757026</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5397747070139503</v>
+        <v>-0.5407241579324098</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.03886726529482824</v>
+        <v>-0.00252836549495955</v>
       </c>
     </row>
   </sheetData>
